--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findMemberById-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findMemberById-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
   <si>
     <t>Statement: UserRepository.findMemberById(memberId) – retrieves a Member record by its ID. Throws NotFoundError if not found.</t>
   </si>
@@ -121,7 +121,10 @@
     <t>memberId = ""</t>
   </si>
   <si>
-    <t>memberId = "a"</t>
+    <t>memberId = "a" (inex)</t>
+  </si>
+  <si>
+    <t>memberId = "a" (exist)</t>
   </si>
   <si>
     <t>BVA</t>
@@ -130,7 +133,16 @@
     <t>BVA-1 Empty</t>
   </si>
   <si>
-    <t>BVA-2 OneChar</t>
+    <t>BVA-2 InexChar</t>
+  </si>
+  <si>
+    <t>memberId = "a" (not in DB)</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistChar</t>
+  </si>
+  <si>
+    <t>memberId = "a" (in DB)</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -154,7 +166,13 @@
     <t>BVA-2</t>
   </si>
   <si>
-    <t>One char memberId</t>
+    <t>One char (inex)</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>One char (exist)</t>
   </si>
   <si>
     <t>Testing</t>
@@ -839,7 +857,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -880,6 +898,17 @@
         <v>34</v>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -888,7 +917,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -903,7 +932,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -920,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
@@ -937,15 +966,32 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -957,7 +1003,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -973,10 +1019,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>20</v>
@@ -999,7 +1045,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>25</v>
@@ -1019,7 +1065,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -1036,10 +1082,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
@@ -1056,15 +1102,35 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="F5" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="5" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1093,16 +1159,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1110,45 +1176,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="B3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1157,19 +1223,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findMemberById-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/findMemberById-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="66">
-  <si>
-    <t>Statement: UserRepository.findMemberById(memberId) – retrieves a Member record by its ID. Throws NotFoundError if not found.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="58">
+  <si>
+    <t>Statement: UserRepository.findMemberById(id) – Retrieves a member by ID. Returns the MemberWithUser on success. Throws NotFoundError if no member exists with the given ID.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string</t>
+    <t>Input: id: string</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. A member with the given ID may or may not exist.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;MemberWithUser&gt; | throws NotFoundError</t>
+    <t>Output: Promise&lt;MemberWithUser&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>Returns Member record with parent User.</t>
+    <t>On success: MemberWithUser returned with result.id: MEMBER_ID, result.user defined. On failure: NotFoundError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,10 +67,10 @@
     <t>Member existence</t>
   </si>
   <si>
-    <t>Member with given id exists</t>
-  </si>
-  <si>
-    <t>Member does not exist (NotFoundError)</t>
+    <t>Existing ID → MemberWithUser returned</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
   </si>
   <si>
     <t>No TC</t>
@@ -91,10 +91,10 @@
     <t>EC-1</t>
   </si>
   <si>
-    <t>memberId = existing-member-uuid</t>
-  </si>
-  <si>
-    <t>Returns MemberWithUser</t>
+    <t>id: MEMBER_ID</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.id: MEMBER_ID, result.user defined</t>
   </si>
   <si>
     <t>Passed</t>
@@ -103,10 +103,10 @@
     <t>EC-2</t>
   </si>
   <si>
-    <t>memberId = "nonexistent-id"</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: NONEXISTENT_ID</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -118,31 +118,28 @@
     <t>ID length</t>
   </si>
   <si>
-    <t>memberId = ""</t>
-  </si>
-  <si>
-    <t>memberId = "a" (inex)</t>
-  </si>
-  <si>
-    <t>memberId = "a" (exist)</t>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>BVA-2 InexChar</t>
-  </si>
-  <si>
-    <t>memberId = "a" (not in DB)</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistChar</t>
-  </si>
-  <si>
-    <t>memberId = "a" (in DB)</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: ""</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match)</t>
+  </si>
+  <si>
+    <t>id: "a" (found)</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.id: "a"</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -151,30 +148,9 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Existing member ID</t>
-  </si>
-  <si>
-    <t>Non-existent ID</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>Empty memberId</t>
-  </si>
-  <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>One char (inex)</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
-    <t>One char (exist)</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -205,7 +181,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-04</t>
+    <t>REPO-04</t>
   </si>
   <si>
     <t>n/a</t>
@@ -771,7 +747,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
@@ -857,7 +833,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -885,28 +861,6 @@
       </c>
       <c r="C2" s="1" t="s">
         <v>33</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -932,7 +886,7 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>20</v>
@@ -949,10 +903,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>29</v>
@@ -966,10 +920,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>29</v>
@@ -983,13 +937,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="E4" s="5" t="s">
         <v>26</v>
@@ -1019,10 +973,10 @@
         <v>18</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>43</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>20</v>
@@ -1045,7 +999,7 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>25</v>
@@ -1065,7 +1019,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>29</v>
@@ -1082,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>29</v>
@@ -1102,10 +1056,10 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>29</v>
@@ -1122,13 +1076,13 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>26</v>
@@ -1159,16 +1113,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1176,39 +1130,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="B3" s="1">
         <v>5</v>
@@ -1223,19 +1177,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
